--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>426</v>
